--- a/data/excel/RiskEvents.xlsx
+++ b/data/excel/RiskEvents.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -602,9 +602,38 @@
         <v>2026-08-21T15:26:27.192Z</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>EVT-1791222562474-knqe</v>
+      </c>
+      <c r="B8" t="str">
+        <v>REQUEST_CREATED</v>
+      </c>
+      <c r="C8" t="str">
+        <v>yamahasac</v>
+      </c>
+      <c r="D8" t="str">
+        <v>PACK1-VERIFY-123</v>
+      </c>
+      <c r="E8" t="str">
+        <v>0555998877</v>
+      </c>
+      <c r="F8" t="str">
+        <v>DEV-VERIFY-001</v>
+      </c>
+      <c r="G8" t="str">
+        <v>ada41e552a5d4b62df3d77ebd29cd5bf</v>
+      </c>
+      <c r="H8" t="str">
+        <v>{"requestType":"order","score":0,"decision":"ALLOW"}</v>
+      </c>
+      <c r="I8" t="str">
+        <v>2026-10-05T17:49:22.474Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I8"/>
   </ignoredErrors>
 </worksheet>
 </file>